--- a/dev-docs/模型定价.xlsx
+++ b/dev-docs/模型定价.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t/>
   </si>
@@ -76,48 +76,99 @@
     <t>T-C-3-hq</t>
   </si>
   <si>
+    <t>文本对话</t>
+  </si>
+  <si>
+    <t>✅支持</t>
+  </si>
+  <si>
+    <t>Claude Opus 4.8 高性能档；1M 上下文；深度推理与长程 Agent 旗舰，Tool Calling 效率更高</t>
+  </si>
+  <si>
+    <t>按 Token 计费</t>
+  </si>
+  <si>
+    <t>$5.00/百万 Token（≈¥35.8）</t>
+  </si>
+  <si>
+    <t>$25.00/百万 Token（≈¥179）</t>
+  </si>
+  <si>
+    <t>$0.50/百万 Token（≈¥3.58）</t>
+  </si>
+  <si>
     <t>Claude-Opus-4.7-hq</t>
   </si>
   <si>
     <t>T-C-2-hq</t>
   </si>
   <si>
+    <t>Claude Opus 4.7 高性能档；视觉与验证能力增强（Online-Mind2Web 84%）</t>
+  </si>
+  <si>
     <t>Claude-Sonnet-4.6-hq</t>
   </si>
   <si>
     <t>T-C-1 -2-hq</t>
   </si>
   <si>
+    <t>Claude Sonnet 4.6 高性能档；1M 上下文；代码与 Agent 场景最佳性价比</t>
+  </si>
+  <si>
+    <t>$3.00/百万 Token（≈¥21.5）</t>
+  </si>
+  <si>
+    <t>$15.00/百万 Token（≈¥107）</t>
+  </si>
+  <si>
+    <t>$0.30/百万 Token（≈¥2.15）</t>
+  </si>
+  <si>
     <t>Claude-Opus-4.6-hq</t>
   </si>
   <si>
     <t>T-C-1 -1-hq</t>
   </si>
   <si>
+    <t>Claude Opus 4.6 高性能档；100 万 Token 上下文按标准费率计费</t>
+  </si>
+  <si>
     <t>Claude-Opus-4.8</t>
   </si>
   <si>
     <t>T-C-3</t>
   </si>
   <si>
+    <t>Claude Opus 4.8 标准档；1M 上下文；复杂推理、研究与高自主 Agent 首选</t>
+  </si>
+  <si>
     <t>Claude-Opus-4.7</t>
   </si>
   <si>
     <t>T-C-2</t>
   </si>
   <si>
+    <t>Claude Opus 4.7 标准档；Fast 模式 $10/$50；批量处理可再优惠 50%</t>
+  </si>
+  <si>
     <t>Claude-Opus-4.6</t>
   </si>
   <si>
     <t>T-C-1 -1</t>
   </si>
   <si>
+    <t>Claude Opus 4.6 标准档；100 万 Token 上下文；深度推理场景</t>
+  </si>
+  <si>
     <t>Claude-Sonnet-4.6</t>
   </si>
   <si>
     <t>T-C-1 -2</t>
   </si>
   <si>
+    <t>Claude Sonnet 4.6 标准档；1M 上下文；日常 Agent 编码与长文档处理均衡之选</t>
+  </si>
+  <si>
     <t>gpt</t>
   </si>
   <si>
@@ -127,42 +178,171 @@
     <t>I-A-6</t>
   </si>
   <si>
+    <t>图片生成</t>
+  </si>
+  <si>
+    <t>❌不支持</t>
+  </si>
+  <si>
+    <t>OpenAI 图像生成与编辑模型；支持文生图、图生图、局部重绘，多用于电商主图与广告素材</t>
+  </si>
+  <si>
+    <t>按张计费</t>
+  </si>
+  <si>
+    <t>输入图 $5.00/百万 Token（≈¥35.8）</t>
+  </si>
+  <si>
+    <t>输出图 $40.00/百万 Token（约 ¥0.03–0.19/张）</t>
+  </si>
+  <si>
+    <t>图片输入缓存 $1.25/百万 Token（≈¥8.95）</t>
+  </si>
+  <si>
+    <t>约 ¥0.04–0.25/张（按 Token 折算）</t>
+  </si>
+  <si>
     <t>kimi</t>
   </si>
   <si>
     <t>kimi-k3</t>
   </si>
   <si>
+    <t>月之暗面旗舰开源模型，2.8T 参数；1,048,576 Token 上下文；原生视觉；始终开启推理（reasoning_effort 可调）；Agent 并行任务能力强</t>
+  </si>
+  <si>
+    <t>¥20.00/百万 Token（缓存未命中）；¥2.00（缓存命中）</t>
+  </si>
+  <si>
+    <t>¥100.00/百万 Token</t>
+  </si>
+  <si>
+    <t>¥2.00/百万 Token（较未命中降 90%）</t>
+  </si>
+  <si>
     <t>deepseek</t>
   </si>
   <si>
-    <t>文本对话</t>
-  </si>
-  <si>
-    <t>京东云自部署的v4-flash-0731版本</t>
-  </si>
-  <si>
-    <t>V4高性能版本</t>
-  </si>
-  <si>
-    <t>V4快速响应版本</t>
-  </si>
-  <si>
-    <t>V3系列</t>
-  </si>
-  <si>
-    <t>推理增强版</t>
+    <t>jd/deepseek-v4-flash-0731</t>
+  </si>
+  <si>
+    <t>京东云自部署的 v4-flash-0731 版本</t>
+  </si>
+  <si>
+    <t>按次计费</t>
+  </si>
+  <si>
+    <t>—（京东云按次计费，见「次」列）</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>¥0.01/次</t>
+  </si>
+  <si>
+    <t>DeepSeek-V4-Pro</t>
+  </si>
+  <si>
+    <t>✅可选</t>
+  </si>
+  <si>
+    <t>V4 高性能版本；1M 上下文，最大输出 384K；原生支持工具调用与 Anthropic API 标准；并发上限 500 路；支持思考/非思考双模式</t>
+  </si>
+  <si>
+    <t>按 Token 峰谷计费</t>
+  </si>
+  <si>
+    <t>高峰期 ¥9.00/百万 Token；空闲期 ¥4.50（缓存未命中）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥27.00/百万 Token；空闲期 ¥13.50</t>
+  </si>
+  <si>
+    <t>高峰期 ¥0.30/百万 Token；空闲期 ¥0.15（缓存命中）</t>
+  </si>
+  <si>
+    <t>DeepSeek-V4-Flash</t>
+  </si>
+  <si>
+    <t>V4 快速响应版本；1M 上下文；并发上限 2500 路，适合高吞吐调用</t>
+  </si>
+  <si>
+    <t>高峰期 ¥3.00/百万 Token；空闲期 ¥1.50（缓存未命中）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥9.00/百万 Token；空闲期 ¥4.50</t>
+  </si>
+  <si>
+    <t>高峰期 ¥0.10/百万 Token；空闲期 ¥0.05（缓存命中）</t>
+  </si>
+  <si>
+    <t>DeepSeek-V3.2</t>
+  </si>
+  <si>
+    <t>V3 系列；引入稀疏注意力（DSA），长上下文成本更低；160K 上下文</t>
+  </si>
+  <si>
+    <t>¥2.00/百万 Token</t>
+  </si>
+  <si>
+    <t>¥3.00/百万 Token</t>
+  </si>
+  <si>
+    <t>¥1.00/百万 Token</t>
+  </si>
+  <si>
+    <t>DeepSeek-V3-0324</t>
+  </si>
+  <si>
+    <t>V3 系列（2025-03-24 版本）；非推理模型，成本低，适合批量常规任务</t>
+  </si>
+  <si>
+    <t>¥8.00/百万 Token</t>
+  </si>
+  <si>
+    <t>¥0.50/百万 Token</t>
+  </si>
+  <si>
+    <t>DeepSeek-R1-0528</t>
+  </si>
+  <si>
+    <t>推理增强版（2025-05-28 版本）；输出含思维链，适合数学与复杂推理，不支持 Function Call</t>
+  </si>
+  <si>
+    <t>¥4.00/百万 Token</t>
+  </si>
+  <si>
+    <t>¥16.00/百万 Token（含思维链）</t>
+  </si>
+  <si>
+    <t>DeepSeek-OCR2</t>
   </si>
   <si>
     <t>OCR识别</t>
   </si>
   <si>
-    <t>图片文字识别（需特定提示词）</t>
+    <t>图片文字识别（需特定提示词）；开源 3B 模型（Apache 2.0），采用 DeepEncoder V2 视觉因果流，OmniDocBench 91.09 分，支持版面感知 Markdown 导出</t>
+  </si>
+  <si>
+    <t>按 Token 计费 / 自部署</t>
+  </si>
+  <si>
+    <t>约 $0.15/百万 Token（第三方托管）；自部署免费</t>
+  </si>
+  <si>
+    <t>自部署 A100 单页约 ¥0.0008/页</t>
   </si>
   <si>
     <t>DeepSeek-OCR</t>
   </si>
   <si>
+    <t>图片文字识别（需特定提示词）；上一代 DeepSeek-OCR，3B 级模型，支持图像转文本与 Markdown 导出</t>
+  </si>
+  <si>
+    <t>自部署单页约 ¥0.001/页</t>
+  </si>
+  <si>
     <t>仓山人工智能</t>
   </si>
   <si>
@@ -175,318 +355,120 @@
     <t>视频生成</t>
   </si>
   <si>
+    <t>最新一代视频模型；最长 30 秒、最高 1080p；最多 50 个多模态参考素材（图/视频/音频）；新增音频驱动画面、视频局部重绘、延长续写</t>
+  </si>
+  <si>
+    <t>按秒计费（按分辨率折算）</t>
+  </si>
+  <si>
+    <t>无参考视频 70 元/百万 Token；带参考视频 42 元/百万 Token</t>
+  </si>
+  <si>
+    <t>720P 约 ¥1.51/秒；480P 约 ¥0.67/秒；1080P 约 ¥3.74/秒</t>
+  </si>
+  <si>
     <t>doubao-seedance-2.0</t>
   </si>
   <si>
+    <t>视频生成增强版；支持文/图/音/视频四模态输入；最高 4K 输出，单次最长 15 秒</t>
+  </si>
+  <si>
+    <t>2 元/秒（增强版基准）；1.6 元/秒（基础版基准）</t>
+  </si>
+  <si>
+    <t>480P ¥0.56；720P ¥1.21；1080P ¥3.01；4K ¥6.22（元/秒）</t>
+  </si>
+  <si>
     <t>doubao-seedance-2.0-fast</t>
   </si>
   <si>
+    <t>视频生成基础版·快速档；8/7–10/7 期间 480P/720P 享 75 折，折后 720P 约 0.6 元/秒</t>
+  </si>
+  <si>
+    <t>1.6 元/秒（基础版基准）</t>
+  </si>
+  <si>
+    <t>480P ¥0.44；720P ¥0.95（元/秒）</t>
+  </si>
+  <si>
     <t>doubao-seedance-2.0-mini</t>
   </si>
   <si>
+    <t>高性价比轻量版本；4 折活动期间 720P 低至约 0.2 元/秒；适合电商与营销素材批量生产</t>
+  </si>
+  <si>
+    <t>480P ¥0.28；720P ¥0.605（元/秒）</t>
+  </si>
+  <si>
     <t>doubao-seedance-1.5-pro</t>
   </si>
   <si>
+    <t>上一代专业版（官方已公告即将下线）；支持有声/无声视频生成</t>
+  </si>
+  <si>
+    <t>有声视频 ¥0.016/千 Token</t>
+  </si>
+  <si>
+    <t>无声视频 ¥0.008/千 Token</t>
+  </si>
+  <si>
     <t>doubao-seedream-5.0-prodoubao-seedream-5.0-lite</t>
   </si>
   <si>
-    <t>图片生成</t>
+    <t>该行为 5.0 Pro 与 5.0 Lite 两个模型。Pro：4K 写实、中文文字渲染与版式控制最强，支持标记式精准局部编辑；Lite：轻量低成本批量出图</t>
+  </si>
+  <si>
+    <t>输入图首张免费，第 2 张起 ¥0.02/张</t>
+  </si>
+  <si>
+    <t>Pro：≤261 万像素 ¥0.3/张；&gt;261 万像素 ¥0.6/张</t>
+  </si>
+  <si>
+    <t>Lite：¥0.22/张</t>
+  </si>
+  <si>
+    <t>Pro 限流约 500 张/分钟</t>
   </si>
   <si>
     <t>doubao-seedream-4.5</t>
   </si>
   <si>
+    <t>4.5 版本；支持文生图/图生图/多图参考（最多 10 张），最高 4K 输出，主体与光影一致性强</t>
+  </si>
+  <si>
+    <t>首张免费</t>
+  </si>
+  <si>
+    <t>¥0.25/张（文生图/图生图统一）</t>
+  </si>
+  <si>
+    <t>角色图（主图+三视图）折算 ¥0.50/张</t>
+  </si>
+  <si>
     <t>doubao-seedream-4.0</t>
   </si>
   <si>
+    <t>4.0 版本；上一代主力图像模型，性价比高，适合常规商品图与海报批量生成</t>
+  </si>
+  <si>
+    <t>¥0.20/张</t>
+  </si>
+  <si>
     <t>doubao-seedream-3.0</t>
   </si>
   <si>
+    <t>3.0 版本（doubao-seedream-3.0-t2i）；文生图专用，成本最低，适合大批量基础出图</t>
+  </si>
+  <si>
+    <t>¥0.259/张（文生图）</t>
+  </si>
+  <si>
     <t>无</t>
   </si>
   <si>
     <t>subtitle-erase</t>
   </si>
   <si>
-    <t>✅支持</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.8 高性能档；1M 上下文；深度推理与长程 Agent 旗舰，Tool Calling 效率高</t>
-  </si>
-  <si>
-    <t>按 Token 计费</t>
-  </si>
-  <si>
-    <t>$5.00/百万 Token（≈¥35.8）</t>
-  </si>
-  <si>
-    <t>$25.00/百万 Token（≈¥179）</t>
-  </si>
-  <si>
-    <t>$0.50/百万 Token（≈¥3.58）</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.7 高性能档；视觉得分与验证能力增强（Online-Mind2Web 84%）</t>
-  </si>
-  <si>
-    <t>Claude Sonnet 4.6 高性能档；1M 上下文；代码与 Agent 场景最佳性价比</t>
-  </si>
-  <si>
-    <t>$3.00/百万 Token（≈¥21.5）</t>
-  </si>
-  <si>
-    <t>$15.00/百万 Token（≈¥107）</t>
-  </si>
-  <si>
-    <t>$0.30/百万 Token（≈¥2.15）</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.6 高性能档；100 万 Token 上下文按标准费率计费</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.8 标准档；1M 上下文；复杂推理、研究与高自主 Agent 首选</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.7 标准档；Fast 模式 $10/$50；批量处理可再优惠 50%</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.6 标准档；100 万 Token 上下文；深度推理场景</t>
-  </si>
-  <si>
-    <t>Claude Sonnet 4.6 标准档；1M 上下文；日常 Agent 编码与长文档处理均衡之选</t>
-  </si>
-  <si>
-    <t>❌不支持</t>
-  </si>
-  <si>
-    <t>OpenAI 图像生成与编辑模型；支持文生图、图生图、局部重绘，多用于电商主图与广告素材</t>
-  </si>
-  <si>
-    <t>按张计费</t>
-  </si>
-  <si>
-    <t>输入图 $5.00/百万 Token（≈¥35.8）</t>
-  </si>
-  <si>
-    <t>输出图 $40.00/百万 Token（约 ¥0.03–0.19/张）</t>
-  </si>
-  <si>
-    <t>图片输入缓存 $1.25/百万 Token（≈¥8.95）</t>
-  </si>
-  <si>
-    <t>约 ¥0.04–0.25/张（按官方 Token 折算）</t>
-  </si>
-  <si>
-    <t>月之暗面旗舰开源模型，2.8T 参数；1,048,576 Token 上下文；原生视觉；强制推理（reasoning_effort 可调）；Agent 任务并行强</t>
-  </si>
-  <si>
-    <t>¥20.00/百万 Token（缓存未命中）；¥2.00/百万 Token（缓存命中）</t>
-  </si>
-  <si>
-    <t>¥100.00/百万 Token</t>
-  </si>
-  <si>
-    <t>¥2.00/百万 Token（较未命中降 90%）</t>
-  </si>
-  <si>
-    <t>jd/deepseek-v4-flash-0731</t>
-  </si>
-  <si>
-    <t>京东云自部署的 v4-flash-0731 版本</t>
-  </si>
-  <si>
-    <t>按次计费</t>
-  </si>
-  <si>
-    <t>—（京东云按次计费，见「次」列）</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>¥0.01/次</t>
-  </si>
-  <si>
-    <t>DeepSeek-V4-Pro</t>
-  </si>
-  <si>
-    <t>✅可选</t>
-  </si>
-  <si>
-    <t>V4 高性能版本；1M 上下文，最大输出 384K；原生支持工具调用与 Anthropic API 标准；并发上限 500 路。支持「思考/非思考」双模式</t>
-  </si>
-  <si>
-    <t>按 Token 峰谷计费</t>
-  </si>
-  <si>
-    <t>高峰期 ¥9.00/百万 Token；空闲期 ¥4.50（缓存未命中）</t>
-  </si>
-  <si>
-    <t>高峰期 ¥27.00/百万 Token；空闲期 ¥13.50</t>
-  </si>
-  <si>
-    <t>高峰期 ¥0.30/百万 Token；空闲期 ¥0.15（缓存命中）</t>
-  </si>
-  <si>
-    <t>DeepSeek-V4-Flash</t>
-  </si>
-  <si>
-    <t>V4 快速响应版本；1M 上下文；并发上限 2500 路，适合高吞吐调用</t>
-  </si>
-  <si>
-    <t>高峰期 ¥3.00/百万 Token；空闲期 ¥1.50（缓存未命中）</t>
-  </si>
-  <si>
-    <t>高峰期 ¥9.00/百万 Token；空闲期 ¥4.50</t>
-  </si>
-  <si>
-    <t>高峰期 ¥0.10/百万 Token；空闲期 ¥0.05（缓存命中）</t>
-  </si>
-  <si>
-    <t>DeepSeek-V3.2</t>
-  </si>
-  <si>
-    <t>V3 系列；引入稀疏注意力（DSA），长上下文成本更低；160K 上下文</t>
-  </si>
-  <si>
-    <t>¥2.00/百万 Token</t>
-  </si>
-  <si>
-    <t>¥3.00/百万 Token</t>
-  </si>
-  <si>
-    <t>¥1.00/百万 Token</t>
-  </si>
-  <si>
-    <t>DeepSeek-V3-0324</t>
-  </si>
-  <si>
-    <t>V3 系列（2025-03-24 版本）；非推理模型，成本低，适合批量常规任务</t>
-  </si>
-  <si>
-    <t>¥8.00/百万 Token</t>
-  </si>
-  <si>
-    <t>¥0.50/百万 Token</t>
-  </si>
-  <si>
-    <t>DeepSeek-R1-0528</t>
-  </si>
-  <si>
-    <t>推理增强版（2025-05-28 版本）；思维链输出，适合数学与复杂推理，不支持 Function Call</t>
-  </si>
-  <si>
-    <t>¥4.00/百万 Token</t>
-  </si>
-  <si>
-    <t>¥16.00/百万 Token（含思维链）</t>
-  </si>
-  <si>
-    <t>DeepSeek-OCR2</t>
-  </si>
-  <si>
-    <t>图片文字识别（需特定提示词）；开源 3B 模型（Apache 2.0），可采用 DeepEncoder V2 视觉因果流，OmniDocBench 91.09 分，支持版面感知 Markdown 导出</t>
-  </si>
-  <si>
-    <t>按 Token 计费 / 自部署</t>
-  </si>
-  <si>
-    <t>约 $0.15/百万 Token（第三方托管）；自部署免费</t>
-  </si>
-  <si>
-    <t>自部署 A100 单页成本约 ¥0.0008/页</t>
-  </si>
-  <si>
-    <t>图片文字识别（需特定提示词）；上一代 DeepSeek-OCR，3B 级模型，支持图像转文本与 Markdown</t>
-  </si>
-  <si>
-    <t>自部署成本约 ¥0.001/页</t>
-  </si>
-  <si>
-    <t>最新一代视频模型；最长 30 秒、最高 1080p；最多 50 个多模态参考素材（图/视频/音频）；新增音频驱动、视频局部重绘、延长续写</t>
-  </si>
-  <si>
-    <t>按秒计费（按分辨率折算）</t>
-  </si>
-  <si>
-    <t>无参考视频 70 元/百万 Token；带参考视频 42 元/百万 Token</t>
-  </si>
-  <si>
-    <t>720P 约 ¥1.51/秒；480P 约 ¥0.67/秒；1080P 约 ¥3.74/秒</t>
-  </si>
-  <si>
-    <t>视频生成增强版；支持文/图/音/视频四模态输入；最高 4K 输出，单次最长 15 秒</t>
-  </si>
-  <si>
-    <t>2.0 系列单价 2 元/秒（增强版基准）</t>
-  </si>
-  <si>
-    <t>480P ¥0.56；720P ¥1.21；1080P ¥3.01；4K ¥6.22（元/秒）</t>
-  </si>
-  <si>
-    <t>视频生成基础版·快速档；定价 1.6 元/秒基准；8/7–10/7 期间 480P/720P 享 75 折</t>
-  </si>
-  <si>
-    <t>1.6 元/秒（基础版基准）</t>
-  </si>
-  <si>
-    <t>480P ¥0.44；720P ¥0.95（元/秒）；折后约 0.6 元/秒</t>
-  </si>
-  <si>
-    <t>高性价比轻量版本；4 折活动期间 720P 低至约 0.2 元/秒；适合电商与营销素材批量生产</t>
-  </si>
-  <si>
-    <t>480P ¥0.28；720P ¥0.605（元/秒）；折后 720P 约 0.2 元/秒</t>
-  </si>
-  <si>
-    <t>上一代专业版（官方即将下线）；支持有声/无声视频生成</t>
-  </si>
-  <si>
-    <t>有声视频 ¥0.016/千 Token</t>
-  </si>
-  <si>
-    <t>无声视频 ¥0.008/千 Token</t>
-  </si>
-  <si>
-    <t>5.0 Pro 与 5.0 Lite 合并单元格。Pro：4K 写实、中文文字渲染与版式控制最强，支持标记式精准局部编辑；Lite：轻量低成本批量出图</t>
-  </si>
-  <si>
-    <t>输入图首张免费，第 2 张起 ¥0.02/张</t>
-  </si>
-  <si>
-    <t>Pro：≤261 万像素 ¥0.3/张；&gt;261 万像素 ¥0.6/张</t>
-  </si>
-  <si>
-    <t>Lite：¥0.22/张</t>
-  </si>
-  <si>
-    <t>Pro 约 500 张/分钟限流；Lite 同价 ¥0.22/张</t>
-  </si>
-  <si>
-    <t>4.5 版本；支持文生图/图生图/多图参考（最多 10 张），最高 4K 输出，主体与光影一致性强</t>
-  </si>
-  <si>
-    <t>首张免费</t>
-  </si>
-  <si>
-    <t>¥0.25/张（文生图/图生图统一）</t>
-  </si>
-  <si>
-    <t>角色图（主图+三视图）折算 ¥0.50/张</t>
-  </si>
-  <si>
-    <t>4.0 版本；上一代主力图像模型，性价比高，适合常规商品图与海报批量生成</t>
-  </si>
-  <si>
-    <t>¥0.20/张</t>
-  </si>
-  <si>
-    <t>3.0 版本（doubao-seedream-3.0-t2i）；文生图专用，成本最低，适合大批量基础出图</t>
-  </si>
-  <si>
-    <t>¥0.259/张（文生图）</t>
-  </si>
-  <si>
     <t>视频编辑</t>
   </si>
   <si>
@@ -499,220 +481,55 @@
     <t>火山引擎 ¥0.40/分钟（标准版）；¥1.00/分钟（精细化版）</t>
   </si>
   <si>
-    <t>第三方托管 $0.015/秒（≈¥0.108/秒，¥6.5/分钟）</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.8 高性能档；1M 上下文；深度推理与长程 Agent 旗舰，Tool Calling 效率更高</t>
-  </si>
-  <si>
-    <t>Claude Opus 4.7 高性能档；视觉与验证能力增强（Online-Mind2Web 84%）</t>
-  </si>
-  <si>
-    <t>约 ¥0.04–0.25/张（按 Token 折算）</t>
-  </si>
-  <si>
-    <t>月之暗面旗舰开源模型，2.8T 参数；1,048,576 Token 上下文；原生视觉；始终开启推理（reasoning_effort 可调）；Agent 并行任务能力强</t>
-  </si>
-  <si>
-    <t>¥20.00/百万 Token（缓存未命中）；¥2.00（缓存命中）</t>
-  </si>
-  <si>
-    <t>V4 高性能版本；1M 上下文，最大输出 384K；原生支持工具调用与 Anthropic API 标准；并发上限 500 路；支持思考/非思考双模式</t>
-  </si>
-  <si>
-    <t>推理增强版（2025-05-28 版本）；输出含思维链，适合数学与复杂推理，不支持 Function Call</t>
-  </si>
-  <si>
-    <t>图片文字识别（需特定提示词）；开源 3B 模型（Apache 2.0），采用 DeepEncoder V2 视觉因果流，OmniDocBench 91.09 分，支持版面感知 Markdown 导出</t>
-  </si>
-  <si>
-    <t>自部署 A100 单页约 ¥0.0008/页</t>
-  </si>
-  <si>
-    <t>图片文字识别（需特定提示词）；上一代 DeepSeek-OCR，3B 级模型，支持图像转文本与 Markdown 导出</t>
-  </si>
-  <si>
-    <t>自部署单页约 ¥0.001/页</t>
-  </si>
-  <si>
-    <t>最新一代视频模型；最长 30 秒、最高 1080p；最多 50 个多模态参考素材（图/视频/音频）；新增音频驱动画面、视频局部重绘、延长续写</t>
-  </si>
-  <si>
-    <t>1.6 元/秒（基础版基准）；2 元/秒（增强版基准）</t>
-  </si>
-  <si>
-    <t>视频生成基础版·快速档；8/7–10/7 期间 480P/720P 享 75 折，折后 720P 约 0.6 元/秒</t>
-  </si>
-  <si>
-    <t>480P ¥0.44；720P ¥0.95（元/秒）</t>
-  </si>
-  <si>
-    <t>480P ¥0.28；720P ¥0.605（元/秒）</t>
-  </si>
-  <si>
-    <t>上一代专业版（官方已公告即将下线）；支持有声/无声视频生成</t>
-  </si>
-  <si>
-    <t>该行为 5.0 Pro 与 5.0 Lite 两个模型。Pro：4K 写实、中文文字渲染与版式控制最强，支持标记式精准局部编辑；Lite：轻量低成本批量出图</t>
-  </si>
-  <si>
-    <t>Pro 限流约 500 张/分钟</t>
-  </si>
-  <si>
-    <t>2 元/秒（增强版基准）；1.6 元/秒（基础版基准）</t>
-  </si>
-  <si>
     <t>第三方托管 $0.015/秒（≈¥0.108/秒）</t>
   </si>
   <si>
-    <r>
-      <t>jd/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-        <u/>
-      </rPr>
-      <t>deepseek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-v4-flash-0731</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>支持</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-V4-Pro</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>可选</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-V4-Flash</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-V3.2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-V3-0324</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>❌</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>不支持</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-R1-0528</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DeepSeek</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-        <color rgb="FF232930"/>
-        <sz val="12"/>
-      </rPr>
-      <t>-OCR2</t>
-    </r>
+    <t>缓存读取（命中）</t>
+  </si>
+  <si>
+    <t>缓存写入（未命中/首次写入）</t>
+  </si>
+  <si>
+    <t>$6.25/百万 Token（5 分钟 TTL，≈¥44.8）；$10.00（1 小时 TTL，≈¥71.6）</t>
+  </si>
+  <si>
+    <t>$3.75/百万 Token（5 分钟 TTL，≈¥26.9）；$6.00（1 小时 TTL，≈¥43.0）</t>
+  </si>
+  <si>
+    <t>自动缓存，无单独写入费；写入按正常输入价 $5.00/百万 Token（≈¥35.8）计</t>
+  </si>
+  <si>
+    <t>¥2.00/百万 Token（命中，较未命中降 90%）</t>
+  </si>
+  <si>
+    <t>¥20.00/百万 Token（5 分钟 TTL）；¥40.00（1 小时 TTL）</t>
+  </si>
+  <si>
+    <t>—（按次计费，不涉及 Token 缓存）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥9.00/百万 Token；空闲期 ¥4.50（未命中即写入，无单独写入费）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥0.04/百万 Token；空闲期 ¥0.02（缓存命中）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥2.00/百万 Token；空闲期 ¥1.00（未命中即写入，无单独写入费）</t>
+  </si>
+  <si>
+    <t>¥2.00/百万 Token（未命中即写入，无单独写入费）</t>
+  </si>
+  <si>
+    <t>¥4.00/百万 Token（未命中即写入，无单独写入费）</t>
+  </si>
+  <si>
+    <t>¥20.00/百万 Token（缓存未命中）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥2.00/百万 Token；空闲期 ¥1.00（缓存未命中）</t>
+  </si>
+  <si>
+    <t>高峰期 ¥8.00/百万 Token；空闲期 ¥4.00</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1479,16 +1296,13 @@
     <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1799,15 +1613,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="O36"/>
+  <dimension ref="P36"/>
   <sheetFormatPr defaultColWidth="8.88889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="27.4444" style="20" customWidth="1"/>
+    <col min="3" max="3" width="27.4444" style="19" customWidth="1"/>
     <col min="4" max="4" width="16.6667" customWidth="1"/>
     <col min="5" max="9" width="18.7778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28.8">
+    <row r="1" spans="1:16" ht="28.8">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1845,16 +1659,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
@@ -1871,429 +1688,462 @@
         <v>19</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O2" s="10" t="s"/>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="10" t="s"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="s"/>
       <c r="B3" s="7" t="s"/>
       <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N3" s="10" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O3" s="10" t="s"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="10" t="s"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="7" t="s"/>
       <c r="B4" s="7" t="s"/>
       <c r="C4" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="K4" s="10" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4" s="10" t="s"/>
+        <v>35</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>159</v>
+      </c>
       <c r="O4" s="10" t="s"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" s="10" t="s"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="7" t="s"/>
       <c r="B5" s="7" t="s"/>
       <c r="C5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="L5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="M5" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="10" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O5" s="10" t="s"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5" s="10" t="s"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="7" t="s"/>
       <c r="B6" s="7" t="s"/>
       <c r="C6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" s="10" t="s"/>
+      <c r="N6" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O6" s="10" t="s"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" s="10" t="s"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="7" t="s"/>
       <c r="B7" s="7" t="s"/>
       <c r="C7" s="8" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N7" s="10" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O7" s="10" t="s"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7" s="10" t="s"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="7" t="s"/>
       <c r="B8" s="7" t="s"/>
       <c r="C8" s="8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" s="10" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="O8" s="10" t="s"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="10" t="s"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="7" t="s"/>
       <c r="B9" s="7" t="s"/>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>72</v>
-      </c>
       <c r="L9" s="10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N9" s="10" t="s"/>
+        <v>35</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>159</v>
+      </c>
       <c r="O9" s="10" t="s"/>
-    </row>
-    <row r="10" spans="1:15" ht="17.4">
+      <c r="P9" s="10" t="s"/>
+    </row>
+    <row r="10" spans="1:16" ht="17.4">
       <c r="A10" s="7" t="s"/>
       <c r="B10" s="11" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="L10" s="10" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="O10" s="10" t="s"/>
-    </row>
-    <row r="11" spans="1:15" ht="17.4">
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P10" s="10" t="s"/>
+    </row>
+    <row r="11" spans="1:16" ht="17.4">
       <c r="A11" s="7" t="s"/>
       <c r="B11" s="11" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D11" s="12" t="s"/>
       <c r="E11" s="12" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>165</v>
-      </c>
       <c r="J11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="M11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="N11" s="12" t="s"/>
-      <c r="O11" s="10" t="s"/>
-    </row>
-    <row r="12" spans="1:15" ht="17.4">
+        <v>161</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="O11" s="12" t="s"/>
+      <c r="P11" s="10" t="s"/>
+    </row>
+    <row r="12" spans="1:16" ht="17.4">
       <c r="A12" s="7" t="s"/>
       <c r="B12" s="7" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D12" s="10" t="s"/>
       <c r="E12" s="10" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="10" t="s"/>
-    </row>
-    <row r="13" spans="1:15">
+        <v>163</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="10" t="s"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="7" t="s"/>
       <c r="B13" s="7" t="s"/>
       <c r="C13" s="8" t="s"/>
@@ -2307,47 +2157,51 @@
       <c r="K13" s="10" t="s"/>
       <c r="L13" s="10" t="s"/>
       <c r="M13" s="10" t="s"/>
-      <c r="N13" s="10" t="s"/>
+      <c r="N13" s="17" t="s"/>
       <c r="O13" s="10" t="s"/>
-    </row>
-    <row r="14" spans="1:15" ht="17.4">
+      <c r="P13" s="10" t="s"/>
+    </row>
+    <row r="14" spans="1:16" ht="17.4">
       <c r="A14" s="7" t="s"/>
       <c r="B14" s="7" t="s"/>
       <c r="C14" s="8" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D14" s="10" t="s"/>
       <c r="E14" s="10" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14" s="10" t="s"/>
+        <v>81</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>164</v>
+      </c>
       <c r="O14" s="10" t="s"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14" s="10" t="s"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="7" t="s"/>
       <c r="B15" s="7" t="s"/>
       <c r="C15" s="8" t="s"/>
@@ -2361,47 +2215,51 @@
       <c r="K15" s="10" t="s"/>
       <c r="L15" s="10" t="s"/>
       <c r="M15" s="10" t="s"/>
-      <c r="N15" s="10" t="s"/>
+      <c r="N15" s="17" t="s"/>
       <c r="O15" s="10" t="s"/>
-    </row>
-    <row r="16" spans="1:15" ht="17.4">
+      <c r="P15" s="10" t="s"/>
+    </row>
+    <row r="16" spans="1:16" ht="17.4">
       <c r="A16" s="7" t="s"/>
       <c r="B16" s="7" t="s"/>
       <c r="C16" s="8" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D16" s="10" t="s"/>
       <c r="E16" s="10" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="N16" s="10" t="s"/>
+        <v>165</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>166</v>
+      </c>
       <c r="O16" s="10" t="s"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16" s="10" t="s"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="7" t="s"/>
       <c r="B17" s="7" t="s"/>
       <c r="C17" s="8" t="s"/>
@@ -2415,47 +2273,51 @@
       <c r="K17" s="10" t="s"/>
       <c r="L17" s="10" t="s"/>
       <c r="M17" s="10" t="s"/>
-      <c r="N17" s="10" t="s"/>
+      <c r="N17" s="17" t="s"/>
       <c r="O17" s="10" t="s"/>
-    </row>
-    <row r="18" spans="1:15" ht="17.4">
+      <c r="P17" s="10" t="s"/>
+    </row>
+    <row r="18" spans="1:16" ht="17.4">
       <c r="A18" s="7" t="s"/>
       <c r="B18" s="7" t="s"/>
       <c r="C18" s="8" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D18" s="10" t="s"/>
       <c r="E18" s="10" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="N18" s="10" t="s"/>
+        <v>91</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>167</v>
+      </c>
       <c r="O18" s="10" t="s"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18" s="10" t="s"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="7" t="s"/>
       <c r="B19" s="7" t="s"/>
       <c r="C19" s="8" t="s"/>
@@ -2469,47 +2331,51 @@
       <c r="K19" s="10" t="s"/>
       <c r="L19" s="10" t="s"/>
       <c r="M19" s="10" t="s"/>
-      <c r="N19" s="10" t="s"/>
+      <c r="N19" s="17" t="s"/>
       <c r="O19" s="10" t="s"/>
-    </row>
-    <row r="20" spans="1:15" ht="17.4">
+      <c r="P19" s="10" t="s"/>
+    </row>
+    <row r="20" spans="1:16" ht="17.4">
       <c r="A20" s="7" t="s"/>
       <c r="B20" s="7" t="s"/>
       <c r="C20" s="8" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="D20" s="10" t="s"/>
       <c r="E20" s="10" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N20" s="10" t="s"/>
+        <v>95</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>167</v>
+      </c>
       <c r="O20" s="10" t="s"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20" s="10" t="s"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="7" t="s"/>
       <c r="B21" s="7" t="s"/>
       <c r="C21" s="8" t="s"/>
@@ -2523,47 +2389,51 @@
       <c r="K21" s="10" t="s"/>
       <c r="L21" s="10" t="s"/>
       <c r="M21" s="10" t="s"/>
-      <c r="N21" s="10" t="s"/>
+      <c r="N21" s="17" t="s"/>
       <c r="O21" s="10" t="s"/>
-    </row>
-    <row r="22" spans="1:15" ht="17.4">
+      <c r="P21" s="10" t="s"/>
+    </row>
+    <row r="22" spans="1:16" ht="17.4">
       <c r="A22" s="7" t="s"/>
       <c r="B22" s="7" t="s"/>
       <c r="C22" s="8" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D22" s="10" t="s"/>
       <c r="E22" s="10" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N22" s="10" t="s"/>
       <c r="O22" s="10" t="s"/>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22" s="10" t="s"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="7" t="s"/>
       <c r="B23" s="7" t="s"/>
       <c r="C23" s="8" t="s"/>
@@ -2577,49 +2447,53 @@
       <c r="K23" s="10" t="s"/>
       <c r="L23" s="10" t="s"/>
       <c r="M23" s="10" t="s"/>
-      <c r="N23" s="10" t="s"/>
+      <c r="N23" s="17" t="s"/>
       <c r="O23" s="10" t="s"/>
-    </row>
-    <row r="24" spans="1:15" ht="17.4">
+      <c r="P23" s="10" t="s"/>
+    </row>
+    <row r="24" spans="1:16" ht="17.4">
       <c r="A24" s="7" t="s"/>
       <c r="B24" s="7" t="s"/>
       <c r="C24" s="8" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D24" s="10" t="s"/>
       <c r="E24" s="10" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="O24" s="10" t="s"/>
-    </row>
-    <row r="25" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="P24" s="10" t="s"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="7" t="s"/>
       <c r="B25" s="7" t="s"/>
       <c r="C25" s="8" t="s"/>
@@ -2633,440 +2507,474 @@
       <c r="K25" s="10" t="s"/>
       <c r="L25" s="10" t="s"/>
       <c r="M25" s="10" t="s"/>
-      <c r="N25" s="10" t="s"/>
+      <c r="N25" s="17" t="s"/>
       <c r="O25" s="10" t="s"/>
-    </row>
-    <row r="26" spans="1:15" ht="17.4">
+      <c r="P25" s="10" t="s"/>
+    </row>
+    <row r="26" spans="1:16" ht="17.4">
       <c r="A26" s="7" t="s"/>
       <c r="B26" s="7" t="s"/>
       <c r="C26" s="8" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D26" s="10" t="s"/>
       <c r="E26" s="10" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="O26" s="10" t="s"/>
-    </row>
-    <row r="27" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="P26" s="10" t="s"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="7" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D27" s="10" t="s"/>
       <c r="E27" s="10" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N27" s="10" t="s"/>
-      <c r="O27" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27" s="10" t="s"/>
+      <c r="P27" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="7" t="s"/>
       <c r="B28" s="7" t="s"/>
       <c r="C28" s="8" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="D28" s="10" t="s"/>
       <c r="E28" s="10" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N28" s="10" t="s"/>
-      <c r="O28" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O28" s="10" t="s"/>
+      <c r="P28" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="7" t="s"/>
       <c r="B29" s="7" t="s"/>
       <c r="C29" s="8" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D29" s="10" t="s"/>
       <c r="E29" s="10" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N29" s="10" t="s"/>
-      <c r="O29" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O29" s="10" t="s"/>
+      <c r="P29" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="7" t="s"/>
       <c r="B30" s="7" t="s"/>
       <c r="C30" s="8" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="D30" s="10" t="s"/>
       <c r="E30" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="H30" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N30" s="10" t="s"/>
-      <c r="O30" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O30" s="10" t="s"/>
+      <c r="P30" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="7" t="s"/>
       <c r="B31" s="7" t="s"/>
       <c r="C31" s="8" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="D31" s="10" t="s"/>
       <c r="E31" s="10" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N31" s="10" t="s"/>
+        <v>73</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="O31" s="10" t="s"/>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31" s="10" t="s"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="7" t="s"/>
       <c r="B32" s="7" t="s"/>
       <c r="C32" s="8" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="D32" s="10" t="s"/>
       <c r="E32" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>82</v>
-      </c>
       <c r="K32" s="10" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>147</v>
+        <v>73</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>136</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="7" t="s"/>
       <c r="B33" s="7" t="s"/>
       <c r="C33" s="8" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D33" s="10" t="s"/>
       <c r="E33" s="10" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N33" s="10" t="s"/>
-      <c r="O33" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O33" s="10" t="s"/>
+      <c r="P33" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="7" t="s"/>
       <c r="B34" s="7" t="s"/>
       <c r="C34" s="8" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="D34" s="10" t="s"/>
       <c r="E34" s="10" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N34" s="10" t="s"/>
+        <v>73</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="O34" s="10" t="s"/>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="P34" s="10" t="s"/>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="7" t="s"/>
       <c r="B35" s="7" t="s"/>
       <c r="C35" s="10" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D35" s="10" t="s"/>
       <c r="E35" s="10" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N35" s="10" t="s"/>
+        <v>73</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="O35" s="10" t="s"/>
-    </row>
-    <row r="36" spans="1:15" ht="17.4">
+      <c r="P35" s="10" t="s"/>
+    </row>
+    <row r="36" spans="1:16" ht="17.4">
       <c r="A36" s="7" t="s"/>
       <c r="B36" s="11" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="D36" s="10" t="s"/>
       <c r="E36" s="10" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>160</v>
+        <v>73</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="O36" s="10" t="s">
-        <v>182</v>
+        <v>154</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
